--- a/Clean_data/gold_master_dataset_with_cpi_and_inflation.xlsx
+++ b/Clean_data/gold_master_dataset_with_cpi_and_inflation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Research_Project_colab_TSA_DATA\Clean_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD7A2FF-4A46-40C6-9FE4-98A5D9E4D4C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643FA4AF-7E02-4CD5-AF03-FA3EA1F8E46E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
